--- a/scores_9klasses_new/tables/ids_9klass.xlsx
+++ b/scores_9klasses_new/tables/ids_9klass.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administarator\Desktop\analytics\scores_9klasses_new\tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\analytics\scores_9klasses_new\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF174C4C-E833-4147-BDEC-D57AF677D79D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2266F28-5C0C-4291-BE04-17FAFB400622}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Результат запроса" sheetId="1" r:id="rId1"/>
@@ -391,91 +391,143 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1171</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1173</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1">
+        <v>2423</v>
+      </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1">
+        <v>3007</v>
+      </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1">
+        <v>2289</v>
+      </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1">
+        <v>1251</v>
+      </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1">
+        <v>2357</v>
+      </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>1297</v>
+      </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
+      <c r="A10" s="1">
+        <v>4079</v>
+      </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
+      <c r="A11" s="1">
+        <v>3531</v>
+      </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="A12" s="1">
+        <v>1171</v>
+      </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>1747</v>
+      </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1">
+        <v>3504</v>
+      </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>3373</v>
+      </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+      <c r="A16" s="1">
+        <v>2183</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+      <c r="A17" s="1">
+        <v>2265</v>
+      </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="1">
+        <v>1537</v>
+      </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+      <c r="A19" s="1">
+        <v>2253</v>
+      </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="A20" s="1">
+        <v>2093</v>
+      </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1">
+        <v>1957</v>
+      </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="A22" s="1">
+        <v>2221</v>
+      </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="A23" s="1">
+        <v>1635</v>
+      </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="1">
+        <v>2123</v>
+      </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+      <c r="A25" s="1">
+        <v>1879</v>
+      </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="A26" s="1">
+        <v>1785</v>
+      </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="A27" s="1">
+        <v>3607</v>
+      </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="A28" s="1">
+        <v>1189</v>
+      </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+      <c r="A29" s="1">
+        <v>1765</v>
+      </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
